--- a/Ref docs/Resource/Add Details/Resource Details - Dummy Data.xlsx
+++ b/Ref docs/Resource/Add Details/Resource Details - Dummy Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/anjana_sharma_rockwellautomation_com/Documents/Anjana Sharma - All Important Documents/1. My work/RA Work/AM-APP/Ref docs/Resource/Add Details/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anjana\AM-APP\Ref docs\Resource\Add Details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B4C95BE-0B7C-4FA8-A95F-5FAC923DA1DF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFC7236-EFD0-4306-81A6-756D3FEBC169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="594">
   <si>
     <t>S.NO</t>
   </si>
@@ -56,15 +56,9 @@
     <t>Role/Domain</t>
   </si>
   <si>
-    <t>Previous Workex</t>
-  </si>
-  <si>
     <t>DOJ</t>
   </si>
   <si>
-    <t>Total Workex</t>
-  </si>
-  <si>
     <t>Current Engagement</t>
   </si>
   <si>
@@ -77,24 +71,15 @@
     <t>Implementation</t>
   </si>
   <si>
-    <t>0 years</t>
-  </si>
-  <si>
     <t>2024-07-17</t>
   </si>
   <si>
-    <t>1.83 years</t>
-  </si>
-  <si>
     <t>Devops</t>
   </si>
   <si>
     <t>2019-09-30</t>
   </si>
   <si>
-    <t>6.67 years</t>
-  </si>
-  <si>
     <t>UI</t>
   </si>
   <si>
@@ -110,51 +95,30 @@
     <t>2016-05-23</t>
   </si>
   <si>
-    <t>10 years</t>
-  </si>
-  <si>
     <t>Data Engineer</t>
   </si>
   <si>
     <t>2018-06-01</t>
   </si>
   <si>
-    <t>8 years</t>
-  </si>
-  <si>
     <t>RA Funct| Fine Tuning Large Language Models, RA Funct| Prompt Engineering, RA IT| Amazon DynamoDB, RA IT| Amazon EMR, RA IT| Apache Airflow, RA IT| Azure Cognitive Services, RA IT| Azure Cosmos DB, RA IT| Azure Databricks, RA IT| Azure OpenAI Service, RA IT| Azure Synapse Analytics, RA IT| BERT / GPT models, RA IT| ChatGPT, RA IT| Databricks, RA IT| Databricks Lakehouse, RA IT| Databricks Runtime, RA IT| Delta Lake, RA IT| FastAPI, RA IT| Flask, RA IT| GCP Vertex AI, RA IT| Gemini (Google DeepMind), RA IT| Jupyter Notebooks, RA IT| KubeFlow, RA IT| Kubernetes, RA IT| LangChain, RA IT| OpenAI API, RA IT| OpenAI GPT-4, RA IT| Postgres, RA IT| RAG (Retrieval-Augmented Generation), RA IT| Reidis, RA IT| Streamlit, RA IT| Vector Databases (e.g., FAISS, Milvus, Pinecone)</t>
   </si>
   <si>
     <t>2022-09-01</t>
   </si>
   <si>
-    <t>3.75 years</t>
-  </si>
-  <si>
     <t>Scrum</t>
   </si>
   <si>
-    <t>13years 0months</t>
-  </si>
-  <si>
     <t>2021-05-24</t>
   </si>
   <si>
-    <t>18 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Azure Devops, Customer Success Management (CSM), Project Management, Scrum Methodology, Support Management, Support Team Management</t>
   </si>
   <si>
-    <t>1years 0months</t>
-  </si>
-  <si>
     <t>2020-02-03</t>
   </si>
   <si>
-    <t>7.33 years</t>
-  </si>
-  <si>
     <t>DevOps, MySQL, Software Development, Solution Implementation</t>
   </si>
   <si>
@@ -164,84 +128,51 @@
     <t>2022-08-08</t>
   </si>
   <si>
-    <t>3.83 years</t>
-  </si>
-  <si>
     <t>Data Analysis, Data Modeling, Data Quality, Data Visualization, DAX Language, Logistics, Microsoft Azure, Microsoft Excel, Microsoft Power Business Intelligence (BI), Requirements Gathering, Structured Query Language (SQL), Supply Chain Strategies</t>
   </si>
   <si>
-    <t>0.75 years</t>
-  </si>
-  <si>
     <t>RA IT| Amazon Web Services, RA IT| Cognite, RA IT| FastAPI, RA IT| GitLab, RA IT| JSON, RA IT| Linux, RA IT| MongoDB, RA IT| MS Azure Cloud, RA IT| MS SQL, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| PyTorch, RA IT| REST, RA IT| scikit-learn, RA IT| seaborn, RA IT| SonarQube, RA IT| YAML</t>
   </si>
   <si>
     <t>Backend</t>
   </si>
   <si>
-    <t>2.1 years</t>
-  </si>
-  <si>
     <t>2025-07-07</t>
   </si>
   <si>
-    <t>3.02 years</t>
-  </si>
-  <si>
     <t>Ansible (Software), Artificial Intelligence (AI), AWS DataSync, Data Science, Django Web Framework, Flask (Web Framework), Flask-RESTful, Git, GitHub, GitLab, Linux, Machine Learning (ML), Microsoft Azure, Python (Programming Language), PyTorch, RA IT| Amazon Bedrock, RA IT| Amazon DynamoDB, RA IT| Docker, RA IT| Docker Compose, RA IT| FastAPI, RA IT| Flask, RA IT| Kubernetes, RA IT| Minikube, RA IT| Postgres, Tensorflow, Terraform</t>
   </si>
   <si>
     <t>2021-12-20</t>
   </si>
   <si>
-    <t>4.42 years</t>
-  </si>
-  <si>
     <t>2023-10-06</t>
   </si>
   <si>
-    <t>2.67 years</t>
-  </si>
-  <si>
     <t>Angular, Angular UI, AngularJS, Cascading Style Sheets (CSS), CSS HTML, HTML Web Development, Hyper Text Markup Language (HTML), JavaScript, JSON, RA IT| AngularJS, RA IT| Charts.js, TypeScript</t>
   </si>
   <si>
-    <t>0years 8months</t>
-  </si>
-  <si>
     <t>2022-01-10</t>
   </si>
   <si>
-    <t>5 years</t>
-  </si>
-  <si>
     <t>Bootstrap (Front-End Framework), Debugging, JavaScript, Material UI, ng-bootstrap, RA IT| Angular, RA IT| AngularJS, RA IT| Charts.js, RA IT| ChatGPT, RA IT| D3.js, RA IT| Docker, RA IT| HTML; Java Script; CSS, RA IT| HTML5, RA IT| JSON, RA IT| Web Services, React.js, Software Engineering, TypeScript, Version Control</t>
   </si>
   <si>
     <t>2017-07-10</t>
   </si>
   <si>
-    <t>8.83 years</t>
-  </si>
-  <si>
     <t>RA Funct| Database Implementation, RA Funct| Prompt Engineering, RA Funct| Software Architecture Planning, RA Funct| Software Code Review, RA Funct| Software Development Lifecycle, RA IT| Amazon Web Services, RA IT| Azure Databricks, RA IT| Azure OpenAI Service, RA IT| C/C++, RA IT| ChatGPT, RA IT| Databricks, RA IT| ElasticSearch, RA IT| FastAPI, RA IT| Flask, RA IT| GitLab, RA IT| GraphQL, RA IT| Jira, RA IT| JSON, RA IT| LangChain, RA IT| MongoDB, RA IT| MySQL, RA IT| Object Oriented Programming, RA IT| OpenAI GPT-4, RA IT| Postgres, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| RAG (Retrieval-Augmented Generation), RA IT| Reidis, RA IT| REST, RA IT| SonarQube, RA IT| SQL, RA IT| Vector Databases (e.g., FAISS, Milvus, Pinecone), RA IT| Web Services</t>
   </si>
   <si>
     <t>2022-09-13</t>
   </si>
   <si>
-    <t>3.67 years</t>
-  </si>
-  <si>
     <t>UX</t>
   </si>
   <si>
     <t>2022-06-20</t>
   </si>
   <si>
-    <t>3.92 years</t>
-  </si>
-  <si>
     <t>Design, Information Architecture Design, Prototyping, UI/UX Design, User Experience (UX), User Interface (UI) Design, User Research, User-Centered Design (UCC)</t>
   </si>
   <si>
@@ -254,33 +185,21 @@
     <t>2023-01-02</t>
   </si>
   <si>
-    <t>3.42 years</t>
-  </si>
-  <si>
     <t>Amazon S3, AWS Elastic Kubernetes Service (EKS), Azure App Service, Azure Data Factory, Azure Devops, Azure Kubernetes Service (AKS), DevOps, Docker (Software), Dockerfile, GitLab, GitLab CI/CD, Jenkins Continuous Integration, Kubernetes, Microsoft Azure, Microsoft Azure Application Insights, Microsoft Azure DevOps Pipelines, Microsoft Azure Functions, RA IT| GitLab, Structured Query Language (SQL), Version Control</t>
   </si>
   <si>
     <t>2023-11-20</t>
   </si>
   <si>
-    <t>2.5 years</t>
-  </si>
-  <si>
     <t>GCC Project Manager</t>
   </si>
   <si>
     <t>Project Manager</t>
   </si>
   <si>
-    <t>2years 0months</t>
-  </si>
-  <si>
     <t>2017-09-18</t>
   </si>
   <si>
-    <t>10.67 years</t>
-  </si>
-  <si>
     <t>Amazon Web Services (AWS), Apache Airflow, Apache Solr, Client Service, Cloud Based Services, Cloud Computing Services, Customer Relationship Management (CRM), Databricks Platform, Databricks SQL, ElasticSearch, GraphQL (Query Language), Multiple Project Management, Neo4j Graph Database, Presales Activities, Project Completions, Project Delivery, Project Management Office (PMO), Project Team Leadership, Python (Programming Language), RA IT| MCP, Stakeholder Management, Structured Query Language (SQL)</t>
   </si>
   <si>
@@ -293,42 +212,24 @@
     <t>2017-10-23</t>
   </si>
   <si>
-    <t>8.58 years</t>
-  </si>
-  <si>
     <t>Change Management, Collaboration, Communication, Continuous Improvement, Data-Driven Decision Making, Process Optimization, Project Management, RA Funct| Change Management, RA Funct| Cross-Business Collaboration, RA Funct| Data Migration, RA Funct| Data Visualization, RA Funct| Database Implementation, RA Funct| iPM, PMBOK Methodology, RA Funct| PLM - Application Lifecycle Mgmt, RA Funct| PLM - Change Management, RA Funct| PLM - Configuration Management, RA Funct| PMP Methodology, RA Funct| Process Improvement, RA Funct| Process Mapping, RA Funct| Project Management, RA Funct| Project Scheduling, RA Funct| Project Scoping, RA Funct| Quality Management, RA Funct| Resource Planning, RA Funct| Risk Management, RA Funct| Scope Management, RA Funct| Software Architecture Planning, RA Funct| Software Code Review, RA Funct| Software Development Lifecycle, RA Funct| Software Performance Tuning, RA Funct| Stakeholder Management, RA Funct| Strategic Planning, RA Funct| System Requirement Gathering, RA Funct| Team Leadership, RA Funct| Time Management, RA Ind| Life Sciences General Knowledge, RA Ind| Pharma/BioTech - General Knowledge, RA IT| Amazon Web Services, RA IT| MS PowerBI Reporting, RA IT| PYTHON, RA Prod| FT DataMosaix, Root Cause Problem Solving, Software Application Development, Software Development Management, Waterfall Model</t>
   </si>
   <si>
     <t>2020-08-24</t>
   </si>
   <si>
-    <t>5.75 years</t>
-  </si>
-  <si>
     <t>Python, MySQL, PostgresSQL, FastAPI, REST API, Data Modeling, Software Development, Software Performance Tuning, Code Review, AWS, Elastic search</t>
   </si>
   <si>
-    <t>10years 0months</t>
-  </si>
-  <si>
     <t>2022-03-01</t>
   </si>
   <si>
-    <t>14.25 years</t>
-  </si>
-  <si>
     <t>Project Development, Project Management, Security Engineering, Security Risk, Software Debugging, Software Design, Software Development, Test Design</t>
   </si>
   <si>
-    <t>11years 6months</t>
-  </si>
-  <si>
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>16.33 years</t>
-  </si>
-  <si>
     <t>Budgeting, Consulting, Digital Strategy, Digital Transformation, Enterprise Software as a Service (SaaS), Growth Development, Key Account Development, Management Consulting, Operational Excellence, Project Delivery, Project Management, RA IT| ChatGPT, RA IT| Java/JSP, RA IT| Jira, RA IT| LangChain, RA IT| MCP, RA IT| OpenAI GPT-4, RA IT| Oracle PL/SQL, RA IT| PYTHON, RA IT| R Language, RA IT| RAG (Retrieval-Augmented Generation), RA IT| REST, RA IT| Spring Boot, RA IT| Vector Databases (e.g., FAISS, Milvus, Pinecone), RA IT| XML, Resource Allocation, Solution Consulting, Solutions Delivery, Technical Management</t>
   </si>
   <si>
@@ -353,30 +254,18 @@
     <t>2017-06-05</t>
   </si>
   <si>
-    <t>9 years</t>
-  </si>
-  <si>
     <t>2023-06-30</t>
   </si>
   <si>
-    <t>2.92 years</t>
-  </si>
-  <si>
     <t>Apache Kafka, RA IT| Apache Kafka, RA IT| Docker, RA IT| ElasticSearch, RA IT| FastAPI, RA IT| Kafka Streams, RA IT| KubeFlow, RA IT| Kubernetes, RA IT| MongoDB, RA IT| MySQL, RA IT| Postgres, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| Reidis, RA Prod| FT UnifyTwin</t>
   </si>
   <si>
     <t>2019-12-01</t>
   </si>
   <si>
-    <t>6.5 years</t>
-  </si>
-  <si>
     <t>2019-02-11</t>
   </si>
   <si>
-    <t>7.25 years</t>
-  </si>
-  <si>
     <t>Programming: Python, R, Java - Database: PostgreSQL, MySQL, database design, optimization - Data Engineering: ETL/ELT, data pipelines, data warehousing - Cloud &amp; Integration: AWS, Azure, REST APIs, system integrations</t>
   </si>
   <si>
@@ -386,33 +275,18 @@
     <t>2020-12-21</t>
   </si>
   <si>
-    <t>5.42 years</t>
-  </si>
-  <si>
     <t>python, sql, spark, agentic ai, LLM,</t>
   </si>
   <si>
-    <t>5years 0months</t>
-  </si>
-  <si>
     <t>2016-08-10</t>
   </si>
   <si>
-    <t>14.75 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Amazon Web Services (AWS), Apache Spark, Big Data, Databricks Platform, Information Technology (IT) Projects, Leadership, PostgreSQL, Project Planning, Python (Programming Language), Spark SQL, Structured Query Language (SQL), Team Leadership, Understanding of Requirements</t>
   </si>
   <si>
-    <t>1years 2months</t>
-  </si>
-  <si>
     <t>2019-10-14</t>
   </si>
   <si>
-    <t>7.75 years</t>
-  </si>
-  <si>
     <t>Data Science, Pandas Python Library, PostgreSQL, Python (Programming Language), Python Numpy, RA Funct| Prompt Engineering, RA IT| ChatGPT, RA IT| FastAPI, RA IT| Hugging Face Transformers, RA IT| Jupyter Notebooks, RA IT| LangChain, RA IT| LLaMA (Meta), RA IT| matplotlib, RA IT| OpenAI API, RA IT| Postgres, RA IT| RAG (Retrieval-Augmented Generation), RA IT| seaborn, RA IT| Tableau, RA Prod| FT UnifyTwin, Statistics, Version Control</t>
   </si>
   <si>
@@ -422,30 +296,18 @@
     <t>2021-10-04</t>
   </si>
   <si>
-    <t>4.67 years</t>
-  </si>
-  <si>
     <t>Manual Testing, Project Implementations, Structured Query Language (SQL)</t>
   </si>
   <si>
-    <t>4.83 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Kubernetes, Microsoft Azure, MySQL, Structured Query Language (SQL)</t>
   </si>
   <si>
     <t>C++ Programming Language, Microsoft Azure, MySQL, RA IT| Amazon Web Services, RA IT| Azure Cognitive Services, RA IT| C/C++, RA IT| HTML; Java Script; CSS, RA IT| HTML5, RA IT| JSON, RA IT| MS Azure Cloud, RA IT| MySQL, RA IT| Object Oriented Programming, RA IT| PL-SQL (Oracle), RA IT| SQL, RA Prod| FT UnifyTwin, Structured Query Language (SQL)</t>
   </si>
   <si>
-    <t>3years 0months</t>
-  </si>
-  <si>
     <t>2019-12-09</t>
   </si>
   <si>
-    <t>9.42 years</t>
-  </si>
-  <si>
     <t>Project Management, RA Funct| Change Management, RA Funct| Client Management/Influence, RA Funct| Communication (Written &amp; Verbal), RA Funct| Conflict Resolution, RA Funct| Contract Management, RA Funct| Cross-Business Collaboration, RA Funct| Escalation Management, RA Funct| iPM, PMBOK Methodology, RA Funct| Presentation Delivery, RA Funct| Process Control System Design, RA Funct| Process Improvement, RA Funct| Procurement Management, RA Funct| Project Commissioning, RA Funct| Project Scheduling, RA Funct| Project Scoping, RA Funct| Proposal Development, RA Funct| Quality Management, RA Funct| Resource Planning, RA Funct| Risk Management, RA Funct| Scope Management, RA Funct| Specification Development (URS/FRS/FDS/DS), RA Funct| Stakeholder Management, RA Funct| Strategic Planning, RA Funct| Team Leadership, RA Ind| Chemicals - General Knowledge, RA Ind| Food &amp; Bev - General Knowledge, RA Ind| Life Sciences General Knowledge, RA Ind| Pharma/BioTech - General Knowledge, RA Ind| Pharmaceuticals - Primary (API), RA IT| Apache Kafka, RA IT| Azure Databricks, RA IT| C/C++, RA IT| Docker, RA IT| FastAPI, RA IT| Flask, RA IT| Java/JSP, RA IT| Jupyter Notebooks, RA IT| KubeFlow, RA IT| Kubernetes, RA IT| MongoDB, RA IT| MySQL, RA IT| Postgres, RA IT| PYTHON, RA IT| R Language, RA IT| REST, RA IT| Tableau</t>
   </si>
   <si>
@@ -461,36 +323,21 @@
     <t>Apache Kafka, ASP.NET Core, ASP.NET MVC, C Sharp (Programming Language), ElasticSearch, Microsoft SQL Server, Microsoft SQL Server Management Studio (SSMS), MongoDB, MySQL, OpenTSDB, PostgreSQL, Python (Programming Language), RA IT| FastAPI, RA IT| Flask, Redis, Relational Database Management System (RDBMS), SQL, Stored Procedures, Transact-SQL</t>
   </si>
   <si>
-    <t>0years 4months</t>
-  </si>
-  <si>
     <t>2015-08-10</t>
   </si>
   <si>
-    <t>11.08 years</t>
-  </si>
-  <si>
     <t>Python, AWS, Databricks, Hadoop, Azure IOT, SPARKSQL, MySQL, pyspark,</t>
   </si>
   <si>
     <t>2020-06-01</t>
   </si>
   <si>
-    <t>6 years</t>
-  </si>
-  <si>
     <t>2022-10-03</t>
   </si>
   <si>
-    <t>3 years 0months</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
-    <t>4.92 years</t>
-  </si>
-  <si>
     <t>Data Acquisition (DAQ), IoT Applications, Python (Programming Language), RA Prod| Emulate 3D</t>
   </si>
   <si>
@@ -500,18 +347,12 @@
     <t>2025-05-05</t>
   </si>
   <si>
-    <t>1.08 years</t>
-  </si>
-  <si>
     <t>Application Programming Interface (API), Customer Communications, Data Engineering, Data Integration, Data Modeling, Data Pipelines, Data Processing, Data Warehousing (DW), Documentations, Leadership, Problem Solving, Processing, Project Management, Python (Programming Language), Structured Query Language (SQL)</t>
   </si>
   <si>
     <t>2019-02-18</t>
   </si>
   <si>
-    <t>8.25 years</t>
-  </si>
-  <si>
     <t>Amazon S3, Amazon Simple Email Service (SES), Apache Solr, AWS AI Services, AWS DynamoDB, AWS Fargate, Databricks, DevOps, ETL Development, Generative AI, Google Cloud Platform (GCP), Java, Large Language Model (LLM) Fine-Tuning, Microsoft Azure, MongoDB, MySQL, Prompt Engineering, Python (Programming Language), RA IT| LangChain, Spring Boot</t>
   </si>
   <si>
@@ -521,9 +362,6 @@
     <t>2025-10-06</t>
   </si>
   <si>
-    <t>0.67 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Automated Testing, Cascading Style Sheets (CSS), Generative AI, Hyper Text Markup Language (HTML), Python (Programming Language), Quality Assurance (QA), RA Funct| Model Compression &amp; Quantization, RA Funct| Prompt Engineering, Structured Query Language (SQL)</t>
   </si>
   <si>
@@ -533,9 +371,6 @@
     <t>2019-10-23</t>
   </si>
   <si>
-    <t>6.58 years</t>
-  </si>
-  <si>
     <t>AWS, Databricks, Kubernetes ,GIT , Python,SQL, Kibana, Linux, BigData, ETL, JIRA,Tableau, Microservices, Apache Spark /Pyspark, Agile</t>
   </si>
   <si>
@@ -551,57 +386,36 @@
     <t>Mobile App</t>
   </si>
   <si>
-    <t>3years 2months</t>
-  </si>
-  <si>
     <t>2020-01-20</t>
   </si>
   <si>
-    <t>9.5 years</t>
-  </si>
-  <si>
     <t>Apple Applications, Apple iOS, Data Fusion, iOS Application Development, iOS Development, iOS SDK, Mobile Application Development, Mobile Applications Design, Python (Programming Language), RA Funct| Mobile App Development</t>
   </si>
   <si>
     <t>2019-05-13</t>
   </si>
   <si>
-    <t>7 years</t>
-  </si>
-  <si>
     <t>Azure IoT Edge, C++ Programming Language, Internet of Things (IoT), MySQL, Python (Programming Language), Python Automation, Python Frameworks, Python Requests, Python Software Development, RA Funct| Prompt Engineering, RA IT| Azure OpenAI Service, RA IT| ChatGPT, RA IT| Claude (Anthropic), RA IT| Containerd, RA IT| Docker, RA IT| Docker Compose, RA IT| FastAPI, RA IT| Flask, RA IT| Jupyter Notebooks, RA IT| Kafka Streams, RA IT| LangChain, RA IT| OpenAI API, RA IT| OpenAI GPT-4, RA IT| Postgres, RA IT| RAG (Retrieval-Augmented Generation), RA IT| Vector Databases (e.g., FAISS, Milvus, Pinecone), RA Prod| FT UnifyTwin, Software Debugging, Systems Development</t>
   </si>
   <si>
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2years 8months</t>
-  </si>
-  <si>
     <t>2017-12-07</t>
   </si>
   <si>
-    <t>11.17 years</t>
-  </si>
-  <si>
     <t>AngularJS, Cascading Style Sheets (CSS), Hyper Text Markup Language (HTML), JavaScript, Node.js, React Native, React Redux, React.js, Svelte (Framework)</t>
   </si>
   <si>
     <t>2019-11-20</t>
   </si>
   <si>
-    <t>8.5 years</t>
-  </si>
-  <si>
     <t>React JS, Angular, Javascript, Typescript, NX workspace, HTML, CSS, Bootstrap.</t>
   </si>
   <si>
     <t>2018-04-10</t>
   </si>
   <si>
-    <t>9.08 years</t>
-  </si>
-  <si>
     <t>AJAX (Programming), Amazon S3, Angular, AngularJS, AWS Glue, Databricks Platform, JavaScript, Kubernetes, PostgreSQL, Python (Programming Language), React.js, Redux (Javascript Library), TypeScript, Vanilla JavaScript</t>
   </si>
   <si>
@@ -617,9 +431,6 @@
     <t>2020-09-23</t>
   </si>
   <si>
-    <t>5.67 years</t>
-  </si>
-  <si>
     <t>RA Funct| Prompt Engineering, RA IT| AWS CodeWhisperer, RA IT| ChatGPT, RA IT| Flask, RA IT| Postgres, RA IT| RAG (Retrieval-Augmented Generation), RA Prod| FT UnifyTwin</t>
   </si>
   <si>
@@ -629,27 +440,15 @@
     <t>RA IT| FastAPI, RA IT| Flask, RA IT| Kafka Streams, RA IT| Postgres</t>
   </si>
   <si>
-    <t>18years 0months</t>
-  </si>
-  <si>
     <t>2018-12-22</t>
   </si>
   <si>
-    <t>25.42 years</t>
-  </si>
-  <si>
     <t>2017-12-18</t>
   </si>
   <si>
-    <t>8.42 years</t>
-  </si>
-  <si>
     <t>Microservices Architecture, Software Design, Software Engineering</t>
   </si>
   <si>
-    <t>10.42 years</t>
-  </si>
-  <si>
     <t>Databricks Platform support, Linux Platform support ,Airflow,AWS services ,Kafka, Hadoop Administration</t>
   </si>
   <si>
@@ -662,15 +461,9 @@
     <t>Data Engineering, Data Pipelines, Debugging, Documentations, People Management, Python (Programming Language), RA IT| FastAPI, Structured Query Language (SQL), Teamwork, Time Management, Translations, Writing</t>
   </si>
   <si>
-    <t>0years 7months</t>
-  </si>
-  <si>
     <t>Power BI, SQL, Python, AWS</t>
   </si>
   <si>
-    <t>3 years 0 months</t>
-  </si>
-  <si>
     <t>2024-07-08</t>
   </si>
   <si>
@@ -680,24 +473,12 @@
     <t>Agile Methodology, AI Agents, AI Prompting, Algorithms, Apache JMeter, API Development, API Management, API Testing, Artificial Intelligence (AI), Back-End Development, Cloud Based Solutions, Code Reviews, Computer Science, Conversational AI, Data Analysis, Data Engineering, Data Mining, Data Pipelines, Data Science, Datasets, Generative AI, Intelligent Agents, Machine Learning (ML), Microsoft Power Business Intelligence (BI), MongoDB, MQTT (Message Queuing Telemetry Transport), Oracle, Python (Programming Language), Python for Data Analysis, Python Matplotlib, Python Numpy, Python Sqlite3, Quality Assurance (QA), RA Funct| Data Management Practices, RA Funct| Data Science Tools Knowledge / Usage, RA Funct| Data Visualization, RA Funct| Deep Learning Design / Train, RA Funct| Fine Tuning Large Language Models, RA Funct| Machine Learning (ML) Design, RA Funct| Prompt Engineering, RA Funct| Software Code Review, RA Funct| Software Performance Tuning, RA Funct| Software Testing, RA Funct| Statistical Analysis, RA IT| AutoML (H2O, TPOT, AutoKeras, etc.), RA IT| Azure Machine Learning, RA IT| BERT / GPT models, RA IT| ChatGPT, RA IT| Claude (Anthropic), RA IT| DALL·E, RA IT| Gemini (Google DeepMind), RA IT| Hugging Face Transformers, RA IT| Jupyter Notebooks, RA IT| Keras, RA IT| LangChain, RA IT| LLaMA (Meta), RA IT| LlamaIndex, RA IT| MongoDB, RA IT| MS SQL, RA IT| MySQL, RA IT| OpenAI API, RA IT| OpenAI GPT-4, RA IT| Oracle dB, RA IT| PL-SQL (Oracle), RA IT| PostgreSQL, RA IT| RAG (Retrieval-Augmented Generation), RA IT| scikit-learn, RA IT| SQL, RA IT| TensorFlow, RA IT| Vector Databases (e.g., FAISS, Milvus, Pinecone), RA IT| XGBoost, RA Prod| FT DataMosaix, Snowflake (Platform), Software Development, Spreadsheet Software, Structured Query Language (SQL), Virtual Agents</t>
   </si>
   <si>
-    <t>0years 6months</t>
-  </si>
-  <si>
     <t>2016-03-01</t>
   </si>
   <si>
-    <t>10.75 years</t>
-  </si>
-  <si>
-    <t>6years 0months</t>
-  </si>
-  <si>
     <t>2020-01-06</t>
   </si>
   <si>
-    <t>12.42 years</t>
-  </si>
-  <si>
     <t>AI Architecture, AI Programming, AI Systems, Artificial Intelligence (AI), Artificial Intelligence Algorithms, AWS AI Services, Conversational AI, Data Pipelines, Data Science, Data Tools, Data Types, Dataset Management, Generative AI, Microsoft Artificial Intelligence (AI) Builder</t>
   </si>
   <si>
@@ -713,9 +494,6 @@
     <t>2021-09-08</t>
   </si>
   <si>
-    <t>4.75 years</t>
-  </si>
-  <si>
     <t>Manual Testing, MySQL, Project Implementations, Scrum, Software Enhancement, Structured Query Language (SQL)</t>
   </si>
   <si>
@@ -731,54 +509,33 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>3years 5months</t>
-  </si>
-  <si>
-    <t>4.17 years</t>
-  </si>
-  <si>
     <t>AI Agents, Amazon S3, Artificial Intelligence (AI), AWS AI Services, Azure Blob Storage, Cloud Solutions, Cybersecurity, Data Engineering, Data Pipelines, Data Processing, Databricks Platform, Deep Learning, Digital Forensics, Ethical Hacking, ETL Pipelines, Generative AI, Machine Learning (ML), Microsoft Azure, Microsoft Azure Databricks, Microsoft Azure DevOps, Microsoft Azure SQL Database, PL/SQL (Programming Language), Prompt Engineering, PySpark, Python (Programming Language), Structured Query Language (SQL)</t>
   </si>
   <si>
     <t>2019-05-02</t>
   </si>
   <si>
-    <t>7.08 years</t>
-  </si>
-  <si>
     <t>Angular, Bootstrap (Front-End Framework), Cascading Style Sheets (CSS), Hyper Text Markup Language (HTML), JavaScript, React Redux, React.js, Redux (Javascript Library), TypeScript</t>
   </si>
   <si>
-    <t>4 years 8months</t>
-  </si>
-  <si>
     <t>Health Level 7, Java, Linux, MongoDB, MySQL, Python (Programming Language), RA IT| FastAPI, Software as a Service (SaaS), Software Development Life Cycle (SDLC), Structured Query Language (SQL)</t>
   </si>
   <si>
     <t>Building Dashboards, Data Annotation, Data Visualization, DBeaver, GitHub, GitHub Repositories, Microsoft Azure, MongoDB, Pandas Python Library, Postman (Software), RA IT| Cognite, RA IT| FastAPI, RA IT| HTML; Java Script; CSS, RA IT| JSON, RA IT| Jupyter Notebooks, RA IT| MongoDB, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| REST, RA IT| SQL, RA Prod| FT DataMosaix, RA Prod| FT UnifyTwin, Report Building, SQL Databases, SQLite</t>
   </si>
   <si>
-    <t>1years 1months</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
     <t>RA Funct| Data Visualization, RA Funct| Database Implementation, RA IT| MS SQL, RA IT| MySQL, RA IT| PostgreSQL, RA IT| SQL</t>
   </si>
   <si>
-    <t>2years 1months</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
     <t>2021-11-22</t>
   </si>
   <si>
-    <t>4.5 years</t>
-  </si>
-  <si>
     <t>2019-12-30</t>
   </si>
   <si>
@@ -788,9 +545,6 @@
     <t>HTML5, React.js, TypeScript</t>
   </si>
   <si>
-    <t>1years 5months</t>
-  </si>
-  <si>
     <t>2022-05-09</t>
   </si>
   <si>
@@ -800,9 +554,6 @@
     <t>Android Software Development, iOS Development, RA Funct| Mobile App Development</t>
   </si>
   <si>
-    <t>1years 8months</t>
-  </si>
-  <si>
     <t>2018-12-18</t>
   </si>
   <si>
@@ -815,9 +566,6 @@
     <t>2019-10-22</t>
   </si>
   <si>
-    <t>8.67 years</t>
-  </si>
-  <si>
     <t>React.js, Angular 2+</t>
   </si>
   <si>
@@ -845,9 +593,6 @@
     <t>Agile Methodology, Internet of Things (IoT), Java, JavaScript, Microsoft Azure, Structured Query Language (SQL)</t>
   </si>
   <si>
-    <t>1years 6months</t>
-  </si>
-  <si>
     <t>2024-01-10</t>
   </si>
   <si>
@@ -866,15 +611,9 @@
     <t>2022-06-06</t>
   </si>
   <si>
-    <t>4 years</t>
-  </si>
-  <si>
     <t>2020-11-18</t>
   </si>
   <si>
-    <t>5.5 years</t>
-  </si>
-  <si>
     <t>Amazon S3, Apache Airflow, AWS Glue, Python (Programming Language), SQL</t>
   </si>
   <si>
@@ -884,9 +623,6 @@
     <t>Databricks Platform, PySpark, Python (Programming Language), Structured Query Language (SQL), Team Management</t>
   </si>
   <si>
-    <t>0 years 3 months</t>
-  </si>
-  <si>
     <t>Budgeting, Client Service, Courage, Cultivates innovation, Customer focus, Project Delivery, Project Handling, Project Management, Project Management Practices, RA IT| Amazon Web Services, RA IT| Apache (Casandra, Hadoop, Hive), RA IT| Apache Kafka, RA IT| Apache Spark, RA IT| Apache SparkML, RA IT| Apache Tomcat, RA IT| Azure Machine Learning, RA IT| Data Modeling, RA IT| Eclipse, RA IT| ElasticSearch, RA IT| GitLab, RA IT| Google Cloud Platform, RA IT| H2O, RA IT| Jenkins, RA IT| Jira, RA IT| JSON, RA IT| Linux, RA IT| Linux / Unix, RA IT| Microsoft Azure IOT Hub, RA IT| Microsoft Visio, RA IT| MongoDB, RA IT| MS Azure Cloud, RA IT| MS PowerBI Reporting, RA IT| MS SQL, RA IT| MySQL, RA IT| Oracle dB, RA IT| PostgreSQL, RA IT| PYTHON, RA IT| R Language, RA IT| scikit-learn, RA IT| Selenium WebDriver, RA IT| SonarQube, RA IT| TensorFlow, Resource Allocation, Self-development, Situational adaptability, Strategic mindset, Tech savvy</t>
   </si>
   <si>
@@ -899,24 +635,15 @@
     <t>Cascading Style Sheets (CSS), Hyper Text Markup Language (HTML), Java, JavaScript, MongoDB, Python (Programming Language), RA IT| FastAPI, RA IT| Postgres, RA Prod| FT UnifyTwin, React.js</t>
   </si>
   <si>
-    <t>0years 10months</t>
-  </si>
-  <si>
     <t>2024-02-07</t>
   </si>
   <si>
-    <t>3.17 years</t>
-  </si>
-  <si>
     <t>Bootstrap (Front-End Framework), Figma, Front-End Engineering, Java, JavaScript, Material UI, RA IT| AngularJS, RA IT| HTML; Java Script; CSS, RA IT| Postgres, RA IT| Spring Boot, React.js, Redux (Javascript Library), RESTful APIs, TypeScript, User Interfaces (UI), Web Development</t>
   </si>
   <si>
     <t>2021-06-02</t>
   </si>
   <si>
-    <t>3years 4months</t>
-  </si>
-  <si>
     <t>2020-11-10</t>
   </si>
   <si>
@@ -926,18 +653,12 @@
     <t>Debugging, Docker (Software), Docker Container, Generative AI, JavaScript, Kubernetes, RA IT| MongoDB, RA IT| MySQL, RA IT| PostgreSQL, RA IT| PYTHON, REST API Development, RESTful APIs, Software Development</t>
   </si>
   <si>
-    <t>2years 7months</t>
-  </si>
-  <si>
     <t>2019-11-11</t>
   </si>
   <si>
     <t>Apache Airflow, Apache Spark, Azure Data Factory, Databricks, Matillion ETL, Microsoft Azure, Microsoft Azure Databricks, Microsoft Azure SQL Database, Microsoft SQL Server, MySQL, PostgreSQL, Python (Programming Language), Python for Data Analysis, Python Software Development, RA IT| FastAPI, Relational Database Management System (RDBMS), SQL</t>
   </si>
   <si>
-    <t>2years 3months</t>
-  </si>
-  <si>
     <t>2020-08-27</t>
   </si>
   <si>
@@ -947,12 +668,6 @@
     <t>Agile Methodology, Apache Cassandra, Apache Kafka, Atlassian JIRA, Azure IoT Hub, Microsoft Azure, NoSQL Databases, Python (Programming Language), RA IT| FastAPI, RA IT| MongoDB, RA IT| PostgreSQL, RA IT| PYTHON, Redis, Software Development, SQL</t>
   </si>
   <si>
-    <t>4 years 0months</t>
-  </si>
-  <si>
-    <t>5.92 years</t>
-  </si>
-  <si>
     <t>API Development, C++ Programming Language, MySQL, Object-Oriented Programming (OOP) Concepts, Python (Programming Language), Software Engineering</t>
   </si>
   <si>
@@ -968,15 +683,9 @@
     <t>2021-03-15</t>
   </si>
   <si>
-    <t>5.17 years</t>
-  </si>
-  <si>
     <t>AI Agents, AI Systems, Amazon Machine Images (AMI), Amazon S3, Apache Spark, Artificial Intelligence (AI), AWS DynamoDB, AWS Glue, Back-End Development, Data Engineering, Databricks, Databricks Unified Data Analytics Platform, Microsoft Azure, Python (Programming Language), RA Funct| Cloud Development, RA Funct| Project Management, RA Funct| Software Development Lifecycle, RA Funct| Team Leadership, RA IT| Databricks MLflow, RA IT| PYTHON, RA Prod| FT Analytics VisionAI, Snowflake (Platform), Snowflake Data Warehouse, Web APIs</t>
   </si>
   <si>
-    <t>4years 0months</t>
-  </si>
-  <si>
     <t>Azure Data Factory, Business Intelligence (BI), Data Lake, Data Management, Data Modeling, Data Processing, Data Quality, Data Warehousing (DW), Microsoft Azure, MySQL, PostgreSQL, Python (Programming Language), RA IT| Apache Airflow, RA IT| Azure Databricks, RA IT| Azure Synapse Analytics, RA IT| ChatGPT, RA IT| Databricks, RA IT| Databricks Lakehouse, RA IT| Delta Lake, RA IT| Jupyter Notebooks, RA IT| Kafka Streams, RA IT| Postgres, RA IT| Snowflake, RA Prod| FT UnifyTwin, Structured Query Language (SQL)</t>
   </si>
   <si>
@@ -989,51 +698,30 @@
     <t>2015-10-19</t>
   </si>
   <si>
-    <t>10.58 years</t>
-  </si>
-  <si>
     <t>JavaScript, Angular, React, etc.</t>
   </si>
   <si>
     <t>,Amazon Aurora,Amazon S3,API Development,Docker (Software),Microsoft Azure,MongoDB,MySQL,OPC Communications,PostgreSQL,Python (Programming Language),RSLogix 5000,Software Debugging,Software Enhancement,Structured Query Language (SQL),Test Automation Strategy</t>
   </si>
   <si>
-    <t>3years 9months</t>
-  </si>
-  <si>
     <t>2018-11-26</t>
   </si>
   <si>
-    <t>11.25 years</t>
-  </si>
-  <si>
     <t>Agile Methodology, Application Testing, Data Testing, Databricks Platform, Defect Tracking Tools, Functional Testing, Microsoft SQL Server, PostgreSQL, Python (Programming Language), Quality Assurance (QA), Regression Testing, Selenium, Software Quality Assurance (SQA) Testing, Structured Query Language (SQL), Test Analysis, Test Automation, Test Case Creation, Test Case Design, Test Data Management, Test Development, Test Evaluation, Test Execution, Test Planning, Testing Strategies</t>
   </si>
   <si>
     <t>2021-04-12</t>
   </si>
   <si>
-    <t>5.08 years</t>
-  </si>
-  <si>
-    <t>7years 0months</t>
-  </si>
-  <si>
     <t>2019-09-05</t>
   </si>
   <si>
-    <t>13.75 years</t>
-  </si>
-  <si>
     <t>Azure Data Lake, Consulting, Data Lake, Microsoft Business Intelligence (BI) Testing, Microsoft Power Business Intelligence (BI), Microsoft Power Business Intelligence (BI) Data Visualization, Microsoft Power Business Intelligence (BI) Desktop, Microsoft Power Business Intelligence (BI) Premium, Microsoft Power Business Intelligence (BI) Security, Microsoft SQL Server, Project Management, SQL, SQL Databases, Structured Query Language (SQL), Technical Management</t>
   </si>
   <si>
     <t>2021-10-25</t>
   </si>
   <si>
-    <t>4.58 years</t>
-  </si>
-  <si>
     <t>Amazon S3, AWS Elastic Kubernetes Service (EKS), Azure Kubernetes Service (AKS)</t>
   </si>
   <si>
@@ -1046,9 +734,6 @@
     <t>2018-08-16</t>
   </si>
   <si>
-    <t>2 years 7 months</t>
-  </si>
-  <si>
     <t>Bootstrap (Front-End Framework), Git, GitLab, HTML Web Development, Primefaces, RA IT| Angular, RA IT| AngularJS, RA IT| HTML; Java Script; CSS, React.js, Reactive Extensions for JavaScript (RxJS), Responsive Layout, Responsive UI, RESTful Web Services, TypeScript, User Experience (UX), Web Development, Web Services Integration</t>
   </si>
   <si>
@@ -1070,9 +755,6 @@
     <t>2021-02-22</t>
   </si>
   <si>
-    <t>5.25 years</t>
-  </si>
-  <si>
     <t>AWS, Airflow, Linux, Looker Studio</t>
   </si>
   <si>
@@ -1088,9 +770,6 @@
     <t>2021-12-22</t>
   </si>
   <si>
-    <t>7.5 years</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
@@ -2130,12 +1809,24 @@
   </si>
   <si>
     <t>ben.scott@abc.com</t>
+  </si>
+  <si>
+    <t>Previous Workex (Yr)</t>
+  </si>
+  <si>
+    <t>Total Workex (Yr)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2159,7 +1850,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2171,8 +1862,14 @@
         <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2270,11 +1967,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashed">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="dashed">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="dashed">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="dashed">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2301,6 +2013,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2612,9 +2328,9 @@
     <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="9" max="9" width="19.36328125" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="80" customWidth="1"/>
   </cols>
@@ -2639,19 +2355,19 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2662,28 +2378,28 @@
         <v>8198</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>352</v>
+        <v>245</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>353</v>
+        <v>246</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="I2" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K2" s="6"/>
     </row>
@@ -2695,28 +2411,28 @@
         <v>27460</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>354</v>
+        <v>247</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
+      <c r="I3" s="10">
+        <v>6.166666666666667</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K3" s="6"/>
     </row>
@@ -2728,22 +2444,26 @@
         <v>20316</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>356</v>
+        <v>249</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>357</v>
+        <v>250</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K4" s="6"/>
     </row>
@@ -2755,27 +2475,31 @@
         <v>18755</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>358</v>
+        <v>251</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2786,28 +2510,28 @@
         <v>90810</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>361</v>
+        <v>254</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I6" s="10">
+        <v>9.5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K6" s="6"/>
     </row>
@@ -2819,31 +2543,31 @@
         <v>39373</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>362</v>
+        <v>255</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>350</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="10">
+        <v>7.5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2854,28 +2578,28 @@
         <v>19571</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>364</v>
+        <v>257</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="I8" s="10">
+        <v>3.25</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K8" s="6"/>
     </row>
@@ -2887,31 +2611,31 @@
         <v>92836</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>366</v>
+        <v>259</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>367</v>
+        <v>260</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="G9" s="10">
+        <v>13</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="I9" s="10">
+        <v>17.5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2922,31 +2646,31 @@
         <v>20985</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>368</v>
+        <v>261</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
+      </c>
+      <c r="I10" s="10">
+        <v>6.833333333333333</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2957,31 +2681,31 @@
         <v>71204</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>370</v>
+        <v>263</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>371</v>
+        <v>264</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="I11" s="10">
+        <v>3.3333333333333335</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2992,31 +2716,31 @@
         <v>30640</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>372</v>
+        <v>265</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.25</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3027,31 +2751,31 @@
         <v>27550</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>374</v>
+        <v>267</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>375</v>
+        <v>268</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
+      </c>
+      <c r="G13" s="10">
+        <v>2.1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
+      </c>
+      <c r="I13" s="10">
+        <v>3.75</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3062,28 +2786,28 @@
         <v>34996</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>376</v>
+        <v>269</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>377</v>
+        <v>270</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
+      </c>
+      <c r="I14" s="10">
+        <v>3.9166666666666665</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K14" s="6"/>
     </row>
@@ -3095,31 +2819,31 @@
         <v>89502</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>379</v>
+        <v>272</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I15" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3130,31 +2854,31 @@
         <v>2113</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.66666666666666663</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
+      </c>
+      <c r="I16" s="10">
+        <v>4.583333333333333</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3165,31 +2889,31 @@
         <v>45498</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>382</v>
+        <v>275</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>383</v>
+        <v>276</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
+      </c>
+      <c r="I17" s="10">
+        <v>8.4166666666666661</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3200,28 +2924,28 @@
         <v>27233</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>385</v>
+        <v>278</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I18" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K18" s="6"/>
     </row>
@@ -3233,28 +2957,28 @@
         <v>96144</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>386</v>
+        <v>279</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>387</v>
+        <v>280</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="I19" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K19" s="6"/>
     </row>
@@ -3266,31 +2990,31 @@
         <v>57675</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>388</v>
+        <v>281</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>389</v>
+        <v>282</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>67</v>
+        <v>44</v>
+      </c>
+      <c r="I20" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3301,27 +3025,31 @@
         <v>68051</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>390</v>
+        <v>283</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J21" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3332,28 +3060,28 @@
         <v>11758</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>392</v>
+        <v>285</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>393</v>
+        <v>286</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="I22" s="10">
+        <v>3.25</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K22" s="6"/>
     </row>
@@ -3365,31 +3093,31 @@
         <v>84719</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>394</v>
+        <v>287</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>395</v>
+        <v>288</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="I23" s="10">
+        <v>2.9166666666666665</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3400,28 +3128,28 @@
         <v>53167</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>396</v>
+        <v>289</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>397</v>
+        <v>290</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
+      </c>
+      <c r="I24" s="10">
+        <v>2</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K24" s="6"/>
     </row>
@@ -3433,31 +3161,31 @@
         <v>59852</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>398</v>
+        <v>291</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>399</v>
+        <v>292</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
+      </c>
+      <c r="G25" s="10">
+        <v>2</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>80</v>
+        <v>53</v>
+      </c>
+      <c r="I25" s="10">
+        <v>10.166666666666666</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3468,22 +3196,26 @@
         <v>77384</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>400</v>
+        <v>293</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>401</v>
+        <v>294</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J26" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K26" s="6"/>
     </row>
@@ -3495,31 +3227,31 @@
         <v>5792</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>402</v>
+        <v>295</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>403</v>
+        <v>296</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>85</v>
+        <v>57</v>
+      </c>
+      <c r="I27" s="10">
+        <v>8.0833333333333339</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3530,31 +3262,31 @@
         <v>43835</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>404</v>
+        <v>297</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>405</v>
+        <v>298</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>88</v>
+        <v>59</v>
+      </c>
+      <c r="I28" s="10">
+        <v>5.25</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3565,31 +3297,31 @@
         <v>39510</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>407</v>
+        <v>300</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>90</v>
+        <v>32</v>
+      </c>
+      <c r="G29" s="10">
+        <v>10</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
+      </c>
+      <c r="I29" s="10">
+        <v>13.75</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3600,31 +3332,31 @@
         <v>18886</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>408</v>
+        <v>301</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>409</v>
+        <v>302</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>94</v>
+        <v>52</v>
+      </c>
+      <c r="G30" s="10">
+        <v>11.5</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>96</v>
+        <v>63</v>
+      </c>
+      <c r="I30" s="10">
+        <v>15.833333333333334</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3635,31 +3367,31 @@
         <v>77817</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>411</v>
+        <v>304</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="I31" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3670,27 +3402,31 @@
         <v>90496</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>412</v>
+        <v>305</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>413</v>
+        <v>306</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G32" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J32" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3701,31 +3437,31 @@
         <v>45794</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>414</v>
+        <v>307</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>415</v>
+        <v>308</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I33" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3736,31 +3472,31 @@
         <v>97884</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>416</v>
+        <v>309</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>417</v>
+        <v>310</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="I34" s="10">
+        <v>2.9166666666666665</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3771,28 +3507,28 @@
         <v>2652</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>418</v>
+        <v>311</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>105</v>
+        <v>71</v>
+      </c>
+      <c r="I35" s="10">
+        <v>8.5</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K35" s="6"/>
     </row>
@@ -3804,31 +3540,31 @@
         <v>25806</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>420</v>
+        <v>313</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>421</v>
+        <v>314</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
+      </c>
+      <c r="I36" s="10">
+        <v>2.4166666666666665</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3839,28 +3575,28 @@
         <v>15976</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>422</v>
+        <v>315</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>423</v>
+        <v>316</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
+      </c>
+      <c r="I37" s="10">
+        <v>6</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K37" s="6"/>
     </row>
@@ -3872,31 +3608,31 @@
         <v>58903</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>424</v>
+        <v>317</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>425</v>
+        <v>318</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>112</v>
+        <v>75</v>
+      </c>
+      <c r="I38" s="10">
+        <v>6.833333333333333</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3907,28 +3643,28 @@
         <v>75949</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>426</v>
+        <v>319</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>427</v>
+        <v>320</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="G39" s="10">
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>110</v>
+        <v>77</v>
+      </c>
+      <c r="I39" s="10">
+        <v>6.083333333333333</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K39" s="6"/>
     </row>
@@ -3940,31 +3676,31 @@
         <v>73063</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>428</v>
+        <v>321</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>429</v>
+        <v>322</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G40" s="10">
+        <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>116</v>
+        <v>78</v>
+      </c>
+      <c r="I40" s="10">
+        <v>5.333333333333333</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3975,31 +3711,31 @@
         <v>78820</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>430</v>
+        <v>323</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
+      </c>
+      <c r="G41" s="10">
+        <v>5</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>120</v>
+        <v>80</v>
+      </c>
+      <c r="I41" s="10">
+        <v>14.333333333333334</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4010,28 +3746,28 @@
         <v>1515</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>432</v>
+        <v>325</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>433</v>
+        <v>326</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>122</v>
+        <v>46</v>
+      </c>
+      <c r="G42" s="10">
+        <v>1.1666666666666667</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>124</v>
+        <v>82</v>
+      </c>
+      <c r="I42" s="10">
+        <v>7.25</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K42" s="6"/>
     </row>
@@ -4043,25 +3779,29 @@
         <v>40931</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>434</v>
+        <v>327</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>435</v>
+        <v>328</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G43" s="10">
+        <v>0</v>
+      </c>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+      <c r="I43" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J43" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4072,31 +3812,31 @@
         <v>46500</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>436</v>
+        <v>329</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>437</v>
+        <v>330</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G44" s="10">
+        <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I44" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4107,31 +3847,31 @@
         <v>93179</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>438</v>
+        <v>331</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>439</v>
+        <v>332</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G45" s="10">
+        <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>128</v>
+        <v>85</v>
+      </c>
+      <c r="I45" s="10">
+        <v>4.166666666666667</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4142,31 +3882,31 @@
         <v>27223</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>440</v>
+        <v>333</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>441</v>
+        <v>334</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G46" s="10">
+        <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
+      </c>
+      <c r="I46" s="10">
+        <v>4.333333333333333</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4177,28 +3917,28 @@
         <v>59712</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>442</v>
+        <v>335</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>443</v>
+        <v>336</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="10">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>15</v>
+      <c r="I47" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K47" s="6"/>
     </row>
@@ -4210,31 +3950,31 @@
         <v>55338</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>444</v>
+        <v>337</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>445</v>
+        <v>338</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G48" s="10">
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="I48" s="10">
+        <v>2.9166666666666665</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4245,31 +3985,31 @@
         <v>3547</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>446</v>
+        <v>339</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>447</v>
+        <v>340</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>133</v>
+        <v>52</v>
+      </c>
+      <c r="G49" s="10">
+        <v>3</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>135</v>
+        <v>89</v>
+      </c>
+      <c r="I49" s="10">
+        <v>9</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4280,31 +4020,31 @@
         <v>40722</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>449</v>
+        <v>342</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="G50" s="10">
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>67</v>
+        <v>91</v>
+      </c>
+      <c r="I50" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4315,24 +4055,28 @@
         <v>5357</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>451</v>
+        <v>344</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G51" s="10">
+        <v>0</v>
+      </c>
       <c r="H51" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I51" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J51" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K51" s="6"/>
     </row>
@@ -4344,31 +4088,31 @@
         <v>33039</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>452</v>
+        <v>345</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G52" s="10">
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="I52" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4379,31 +4123,31 @@
         <v>59379</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>454</v>
+        <v>347</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>141</v>
+        <v>52</v>
+      </c>
+      <c r="G53" s="10">
+        <v>0.33333333333333331</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>143</v>
+        <v>95</v>
+      </c>
+      <c r="I53" s="10">
+        <v>10.666666666666666</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4414,28 +4158,28 @@
         <v>46868</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>456</v>
+        <v>349</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>457</v>
+        <v>350</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G54" s="10">
+        <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="I54" s="10">
+        <v>5.5</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K54" s="6"/>
     </row>
@@ -4447,28 +4191,28 @@
         <v>44428</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>458</v>
+        <v>351</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>459</v>
+        <v>352</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G55" s="10">
+        <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="I55" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K55" s="6"/>
     </row>
@@ -4480,31 +4224,31 @@
         <v>15650</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>460</v>
+        <v>353</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>461</v>
+        <v>354</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>148</v>
+        <v>10</v>
+      </c>
+      <c r="G56" s="10">
+        <v>3</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>150</v>
+        <v>99</v>
+      </c>
+      <c r="I56" s="10">
+        <v>4.416666666666667</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4515,31 +4259,31 @@
         <v>93552</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>462</v>
+        <v>355</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>463</v>
+        <v>356</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G57" s="10">
+        <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="I57" s="10">
+        <v>7.5</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4550,31 +4294,31 @@
         <v>6445</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>465</v>
+        <v>358</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G58" s="10">
+        <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>154</v>
+        <v>102</v>
+      </c>
+      <c r="I58" s="10">
+        <v>0.58333333333333337</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4585,28 +4329,28 @@
         <v>30659</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>466</v>
+        <v>359</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>467</v>
+        <v>360</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G59" s="10">
+        <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I59" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K59" s="6"/>
     </row>
@@ -4618,31 +4362,31 @@
         <v>74282</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="G60" s="10">
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="I60" s="10">
+        <v>7.75</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4653,27 +4397,29 @@
         <v>90821</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>470</v>
+        <v>363</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>471</v>
+        <v>364</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G61" s="10">
+        <v>0</v>
       </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
+      <c r="I61" s="10">
+        <v>0</v>
+      </c>
       <c r="J61" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4684,22 +4430,26 @@
         <v>98124</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>472</v>
+        <v>365</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>473</v>
+        <v>366</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="G62" s="10">
+        <v>0</v>
+      </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
+      <c r="I62" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J62" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K62" s="6"/>
     </row>
@@ -4711,31 +4461,31 @@
         <v>22881</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>474</v>
+        <v>367</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>475</v>
+        <v>368</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G63" s="10">
+        <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>161</v>
+        <v>107</v>
+      </c>
+      <c r="I63" s="10">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4746,24 +4496,28 @@
         <v>36338</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>476</v>
+        <v>369</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>477</v>
+        <v>370</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G64" s="10">
+        <v>0</v>
+      </c>
       <c r="H64" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I64" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J64" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K64" s="6"/>
     </row>
@@ -4775,27 +4529,31 @@
         <v>26789</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>478</v>
+        <v>371</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>479</v>
+        <v>372</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G65" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G65" s="10">
+        <v>0</v>
+      </c>
       <c r="H65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J65" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4806,31 +4564,31 @@
         <v>89633</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>481</v>
+        <v>374</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G66" s="10">
+        <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>165</v>
+        <v>110</v>
+      </c>
+      <c r="I66" s="10">
+        <v>6.083333333333333</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>166</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4841,27 +4599,31 @@
         <v>22974</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>482</v>
+        <v>375</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>483</v>
+        <v>376</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G67" s="10">
+        <v>0</v>
+      </c>
       <c r="H67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I67" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J67" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4872,31 +4634,31 @@
         <v>7772</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>484</v>
+        <v>377</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>485</v>
+        <v>378</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G68" s="10">
+        <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="I68" s="10">
+        <v>5.5</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4907,27 +4669,31 @@
         <v>11910</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>486</v>
+        <v>379</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>487</v>
+        <v>380</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G69" s="10">
+        <v>0</v>
+      </c>
       <c r="H69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I69" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J69" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4938,31 +4704,31 @@
         <v>67001</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>488</v>
+        <v>381</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>489</v>
+        <v>382</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>171</v>
+        <v>115</v>
+      </c>
+      <c r="G70" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>173</v>
+        <v>116</v>
+      </c>
+      <c r="I70" s="10">
+        <v>9</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4973,31 +4739,31 @@
         <v>95148</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>490</v>
+        <v>383</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>491</v>
+        <v>384</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G71" s="10">
+        <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>176</v>
+        <v>118</v>
+      </c>
+      <c r="I71" s="10">
+        <v>6.5</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5008,28 +4774,28 @@
         <v>3224</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>492</v>
+        <v>385</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>493</v>
+        <v>386</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G72" s="10">
+        <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>15</v>
+        <v>120</v>
+      </c>
+      <c r="I72" s="10">
+        <v>1.59</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K72" s="6"/>
     </row>
@@ -5041,28 +4807,28 @@
         <v>29156</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>494</v>
+        <v>387</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>495</v>
+        <v>388</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="G73" s="10">
+        <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I73" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K73" s="6"/>
     </row>
@@ -5074,31 +4840,31 @@
         <v>63682</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>496</v>
+        <v>389</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>497</v>
+        <v>390</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>179</v>
+        <v>14</v>
+      </c>
+      <c r="G74" s="10">
+        <v>2.6666666666666665</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>181</v>
+        <v>121</v>
+      </c>
+      <c r="I74" s="10">
+        <v>10.666666666666666</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5109,31 +4875,31 @@
         <v>93324</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>498</v>
+        <v>391</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>499</v>
+        <v>392</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
+      </c>
+      <c r="G75" s="10">
+        <v>2</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>184</v>
+        <v>123</v>
+      </c>
+      <c r="I75" s="10">
+        <v>8</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5144,31 +4910,31 @@
         <v>76607</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>500</v>
+        <v>393</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>501</v>
+        <v>394</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="G76" s="10">
+        <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>187</v>
+        <v>125</v>
+      </c>
+      <c r="I76" s="10">
+        <v>8.6666666666666661</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5179,31 +4945,31 @@
         <v>31228</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>502</v>
+        <v>395</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>503</v>
+        <v>396</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="G77" s="10">
+        <v>0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>58</v>
+        <v>127</v>
+      </c>
+      <c r="I77" s="10">
+        <v>4.5</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5214,27 +4980,31 @@
         <v>41836</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>504</v>
+        <v>397</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>505</v>
+        <v>398</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G78" s="10">
+        <v>0</v>
+      </c>
       <c r="H78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I78" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I78" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J78" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>191</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5245,31 +5015,31 @@
         <v>17431</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>506</v>
+        <v>399</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>507</v>
+        <v>400</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G79" s="10">
+        <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>193</v>
+        <v>130</v>
+      </c>
+      <c r="I79" s="10">
+        <v>5.166666666666667</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5280,31 +5050,31 @@
         <v>66356</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>508</v>
+        <v>401</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>509</v>
+        <v>402</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G80" s="10">
+        <v>0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="I80" s="10">
+        <v>2.9166666666666665</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>195</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5315,31 +5085,31 @@
         <v>34622</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>510</v>
+        <v>403</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>511</v>
+        <v>404</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G81" s="10">
+        <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I81" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5350,28 +5120,28 @@
         <v>27043</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>512</v>
+        <v>405</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>513</v>
+        <v>406</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>197</v>
+        <v>52</v>
+      </c>
+      <c r="G82" s="10">
+        <v>18</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>199</v>
+        <v>134</v>
+      </c>
+      <c r="I82" s="10">
+        <v>24.916666666666668</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K82" s="6"/>
     </row>
@@ -5383,31 +5153,31 @@
         <v>14409</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>514</v>
+        <v>407</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>515</v>
+        <v>408</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G83" s="10">
+        <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>201</v>
+        <v>135</v>
+      </c>
+      <c r="I83" s="10">
+        <v>7.916666666666667</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5418,31 +5188,31 @@
         <v>82194</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>516</v>
+        <v>409</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>517</v>
+        <v>410</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
+      </c>
+      <c r="G84" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>203</v>
+        <v>104</v>
+      </c>
+      <c r="I84" s="10">
+        <v>9.9166666666666661</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>204</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5453,27 +5223,31 @@
         <v>42441</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>518</v>
+        <v>411</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>519</v>
+        <v>412</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G85" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G85" s="10">
+        <v>0</v>
+      </c>
       <c r="H85" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I85" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J85" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>205</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5484,31 +5258,31 @@
         <v>86875</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>520</v>
+        <v>413</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>521</v>
+        <v>414</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G86" s="10">
+        <v>0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I86" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5519,27 +5293,31 @@
         <v>45922</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>522</v>
+        <v>415</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>523</v>
+        <v>416</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G87" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G87" s="10">
+        <v>0</v>
+      </c>
       <c r="H87" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I87" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J87" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5550,31 +5328,31 @@
         <v>88345</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>524</v>
+        <v>417</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>525</v>
+        <v>418</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>208</v>
+        <v>32</v>
+      </c>
+      <c r="G88" s="10">
+        <v>0.58333333333333337</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>130</v>
+        <v>61</v>
+      </c>
+      <c r="I88" s="10">
+        <v>4.333333333333333</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>209</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5585,31 +5363,31 @@
         <v>40320</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>526</v>
+        <v>419</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>527</v>
+        <v>420</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>210</v>
+        <v>10</v>
+      </c>
+      <c r="G89" s="10">
+        <v>3</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
+      </c>
+      <c r="I89" s="10">
+        <v>4.416666666666667</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5620,31 +5398,31 @@
         <v>73504</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>528</v>
+        <v>421</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>529</v>
+        <v>422</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G90" s="10">
+        <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="I90" s="10">
+        <v>0.25</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5655,28 +5433,28 @@
         <v>31844</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>530</v>
+        <v>423</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>531</v>
+        <v>424</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>214</v>
+        <v>52</v>
+      </c>
+      <c r="G91" s="10">
+        <v>0.5</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>216</v>
+        <v>145</v>
+      </c>
+      <c r="I91" s="10">
+        <v>10.25</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K91" s="6"/>
     </row>
@@ -5688,28 +5466,28 @@
         <v>68174</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>532</v>
+        <v>425</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>533</v>
+        <v>426</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G92" s="10">
+        <v>0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I92" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K92" s="6"/>
     </row>
@@ -5721,31 +5499,31 @@
         <v>69439</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>535</v>
+        <v>428</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>217</v>
+        <v>55</v>
+      </c>
+      <c r="G93" s="10">
+        <v>6</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>219</v>
+        <v>146</v>
+      </c>
+      <c r="I93" s="10">
+        <v>11.916666666666666</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>220</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5756,31 +5534,31 @@
         <v>32396</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>536</v>
+        <v>429</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>537</v>
+        <v>430</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G94" s="10">
+        <v>0</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I94" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5791,28 +5569,28 @@
         <v>25353</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>538</v>
+        <v>431</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>539</v>
+        <v>432</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G95" s="10">
+        <v>0</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="I95" s="10">
+        <v>2.9166666666666665</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K95" s="6"/>
     </row>
@@ -5824,31 +5602,31 @@
         <v>43468</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>540</v>
+        <v>433</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>541</v>
+        <v>434</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G96" s="10">
+        <v>0</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="I96" s="10">
+        <v>0.25</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5859,31 +5637,31 @@
         <v>82236</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>542</v>
+        <v>435</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>543</v>
+        <v>436</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G97" s="10">
+        <v>0</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="I97" s="10">
+        <v>3.3333333333333335</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5894,31 +5672,31 @@
         <v>51756</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>544</v>
+        <v>437</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G98" s="10">
+        <v>0</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>225</v>
+        <v>151</v>
+      </c>
+      <c r="I98" s="10">
+        <v>4.25</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5929,25 +5707,29 @@
         <v>75517</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>546</v>
+        <v>439</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>547</v>
+        <v>440</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G99" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G99" s="10">
+        <v>0</v>
+      </c>
       <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="I99" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J99" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5958,31 +5740,31 @@
         <v>57438</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>548</v>
+        <v>441</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>549</v>
+        <v>442</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="G100" s="10">
+        <v>0</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
+      </c>
+      <c r="I100" s="10">
+        <v>10.583333333333334</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5993,28 +5775,28 @@
         <v>6309</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>550</v>
+        <v>443</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>551</v>
+        <v>444</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G101" s="10">
+        <v>0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>225</v>
+        <v>156</v>
+      </c>
+      <c r="I101" s="10">
+        <v>4.333333333333333</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K101" s="6"/>
     </row>
@@ -6026,31 +5808,31 @@
         <v>90925</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>552</v>
+        <v>445</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>553</v>
+        <v>446</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>231</v>
+        <v>19</v>
+      </c>
+      <c r="G102" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>232</v>
+        <v>15</v>
+      </c>
+      <c r="I102" s="10">
+        <v>3.75</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K102" s="6" t="s">
-        <v>233</v>
+        <v>157</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6061,31 +5843,31 @@
         <v>56155</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>554</v>
+        <v>447</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>555</v>
+        <v>448</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G103" s="10">
+        <v>0</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>235</v>
+        <v>158</v>
+      </c>
+      <c r="I103" s="10">
+        <v>6.583333333333333</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>236</v>
+        <v>159</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6096,31 +5878,31 @@
         <v>31058</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>557</v>
+        <v>450</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>237</v>
+        <v>10</v>
+      </c>
+      <c r="G104" s="10">
+        <v>4.666666666666667</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="I104" s="10">
+        <v>6.083333333333333</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>238</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6131,31 +5913,31 @@
         <v>58349</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>558</v>
+        <v>451</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>559</v>
+        <v>452</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G105" s="10">
+        <v>0</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I105" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>239</v>
+        <v>161</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6166,31 +5948,31 @@
         <v>30628</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>560</v>
+        <v>453</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>561</v>
+        <v>454</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>240</v>
+        <v>10</v>
+      </c>
+      <c r="G106" s="10">
+        <v>1.0833333333333333</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>107</v>
+        <v>162</v>
+      </c>
+      <c r="I106" s="10">
+        <v>2.4166666666666665</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>242</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6201,28 +5983,28 @@
         <v>9696</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>562</v>
+        <v>455</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>563</v>
+        <v>456</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>243</v>
+        <v>10</v>
+      </c>
+      <c r="G107" s="10">
+        <v>2.0833333333333335</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>67</v>
+        <v>162</v>
+      </c>
+      <c r="I107" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K107" s="6"/>
     </row>
@@ -6234,28 +6016,28 @@
         <v>69642</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>564</v>
+        <v>457</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>565</v>
+        <v>458</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>13</v>
+        <v>164</v>
+      </c>
+      <c r="G108" s="10">
+        <v>0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
+      </c>
+      <c r="I108" s="10">
+        <v>6</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K108" s="6"/>
     </row>
@@ -6267,28 +6049,28 @@
         <v>30146</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>566</v>
+        <v>459</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>567</v>
+        <v>460</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G109" s="10">
+        <v>0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>246</v>
+        <v>165</v>
+      </c>
+      <c r="I109" s="10">
+        <v>4</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K109" s="6"/>
     </row>
@@ -6300,28 +6082,28 @@
         <v>32245</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>568</v>
+        <v>461</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>569</v>
+        <v>462</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>133</v>
+        <v>43</v>
+      </c>
+      <c r="G110" s="10">
+        <v>3</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>135</v>
+        <v>166</v>
+      </c>
+      <c r="I110" s="10">
+        <v>8.9166666666666661</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K110" s="6"/>
     </row>
@@ -6333,27 +6115,29 @@
         <v>81456</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>570</v>
+        <v>463</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>571</v>
+        <v>464</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G111" s="10">
+        <v>0</v>
       </c>
       <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
+      <c r="I111" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J111" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6364,24 +6148,28 @@
         <v>74027</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>572</v>
+        <v>465</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>573</v>
+        <v>466</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G112" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G112" s="10">
+        <v>0</v>
+      </c>
       <c r="H112" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I112" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I112" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J112" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K112" s="6"/>
     </row>
@@ -6393,31 +6181,31 @@
         <v>84996</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>574</v>
+        <v>467</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>575</v>
+        <v>468</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>231</v>
+        <v>14</v>
+      </c>
+      <c r="G113" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>157</v>
+        <v>63</v>
+      </c>
+      <c r="I113" s="10">
+        <v>7.75</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>249</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6428,28 +6216,28 @@
         <v>93293</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>576</v>
+        <v>469</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>577</v>
+        <v>470</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>250</v>
+        <v>46</v>
+      </c>
+      <c r="G114" s="10">
+        <v>1.4166666666666667</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>116</v>
+        <v>169</v>
+      </c>
+      <c r="I114" s="10">
+        <v>5</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K114" s="6"/>
     </row>
@@ -6461,31 +6249,31 @@
         <v>15793</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>578</v>
+        <v>471</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>579</v>
+        <v>472</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G115" s="10">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H115" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>124</v>
+      <c r="I115" s="10">
+        <v>7.333333333333333</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6496,31 +6284,31 @@
         <v>61183</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>580</v>
+        <v>473</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>581</v>
+        <v>474</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>254</v>
+        <v>46</v>
+      </c>
+      <c r="G116" s="10">
+        <v>1.6666666666666665</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
+      </c>
+      <c r="I116" s="10">
+        <v>8.5833333333333339</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>256</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6531,27 +6319,31 @@
         <v>32019</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>582</v>
+        <v>475</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>583</v>
+        <v>476</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G117" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G117" s="10">
+        <v>0</v>
+      </c>
       <c r="H117" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I117" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I117" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J117" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6562,31 +6354,31 @@
         <v>92516</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>584</v>
+        <v>477</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>585</v>
+        <v>478</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>243</v>
+        <v>14</v>
+      </c>
+      <c r="G118" s="10">
+        <v>2.0833333333333335</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>259</v>
+        <v>175</v>
+      </c>
+      <c r="I118" s="10">
+        <v>8.1666666666666661</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>260</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6597,27 +6389,31 @@
         <v>65974</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>586</v>
+        <v>479</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>587</v>
+        <v>480</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G119" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G119" s="10">
+        <v>0</v>
+      </c>
       <c r="H119" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I119" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I119" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J119" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>261</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6628,31 +6424,31 @@
         <v>71067</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>588</v>
+        <v>481</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>589</v>
+        <v>482</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G120" s="10">
+        <v>0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
+      </c>
+      <c r="I120" s="10">
+        <v>8.5833333333333339</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>263</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6663,31 +6459,31 @@
         <v>9025</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>590</v>
+        <v>483</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>591</v>
+        <v>484</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G121" s="10">
+        <v>0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>235</v>
+        <v>180</v>
+      </c>
+      <c r="I121" s="10">
+        <v>6.583333333333333</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>265</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6698,31 +6494,31 @@
         <v>42171</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>592</v>
+        <v>485</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="G122" s="10">
+        <v>0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>235</v>
+        <v>182</v>
+      </c>
+      <c r="I122" s="10">
+        <v>6.583333333333333</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6733,31 +6529,31 @@
         <v>86147</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>594</v>
+        <v>487</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>595</v>
+        <v>488</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G123" s="10">
+        <v>0</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I123" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>268</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6768,28 +6564,28 @@
         <v>52237</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>596</v>
+        <v>489</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>597</v>
+        <v>490</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>269</v>
+        <v>46</v>
+      </c>
+      <c r="G124" s="10">
+        <v>1.5</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>42</v>
+        <v>185</v>
+      </c>
+      <c r="I124" s="10">
+        <v>3.3333333333333335</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K124" s="6"/>
     </row>
@@ -6801,31 +6597,31 @@
         <v>23220</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>598</v>
+        <v>491</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>599</v>
+        <v>492</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G125" s="10">
+        <v>0</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>52</v>
+        <v>186</v>
+      </c>
+      <c r="I125" s="10">
+        <v>3.9166666666666665</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>272</v>
+        <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6836,31 +6632,31 @@
         <v>30097</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>600</v>
+        <v>493</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>601</v>
+        <v>494</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>13</v>
+        <v>188</v>
+      </c>
+      <c r="G126" s="10">
+        <v>0</v>
       </c>
       <c r="H126" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I126" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K126" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6871,28 +6667,28 @@
         <v>79019</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>602</v>
+        <v>495</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>603</v>
+        <v>496</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G127" s="10">
+        <v>0</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>276</v>
+        <v>190</v>
+      </c>
+      <c r="I127" s="10">
+        <v>3.5</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K127" s="6"/>
     </row>
@@ -6904,31 +6700,31 @@
         <v>2354</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>604</v>
+        <v>497</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>605</v>
+        <v>498</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G128" s="10">
+        <v>0</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>278</v>
+        <v>191</v>
+      </c>
+      <c r="I128" s="10">
+        <v>5</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6939,31 +6735,31 @@
         <v>43632</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>606</v>
+        <v>499</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G129" s="10">
+        <v>0</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
+      </c>
+      <c r="I129" s="10">
+        <v>8.5833333333333339</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>280</v>
+        <v>193</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6974,31 +6770,31 @@
         <v>70624</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>608</v>
+        <v>501</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>609</v>
+        <v>502</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G130" s="10">
+        <v>0</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="I130" s="10">
+        <v>7.5</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>281</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7009,27 +6805,29 @@
         <v>1186</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>610</v>
+        <v>503</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>611</v>
+        <v>504</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>282</v>
+        <v>55</v>
+      </c>
+      <c r="G131" s="10">
+        <v>0.25</v>
       </c>
       <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
+      <c r="I131" s="10">
+        <v>9.4166666666666661</v>
+      </c>
       <c r="J131" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>283</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7040,31 +6838,31 @@
         <v>50680</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>612</v>
+        <v>505</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>613</v>
+        <v>506</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>171</v>
+        <v>55</v>
+      </c>
+      <c r="G132" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>67</v>
+        <v>196</v>
+      </c>
+      <c r="I132" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K132" s="6" t="s">
-        <v>285</v>
+        <v>197</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7075,31 +6873,31 @@
         <v>33552</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>614</v>
+        <v>507</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>615</v>
+        <v>508</v>
       </c>
       <c r="E133" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G133" s="10">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>15</v>
+      <c r="I133" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K133" s="6" t="s">
-        <v>286</v>
+        <v>198</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7110,28 +6908,28 @@
         <v>47264</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>616</v>
+        <v>509</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>617</v>
+        <v>510</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>287</v>
+        <v>46</v>
+      </c>
+      <c r="G134" s="10">
+        <v>0.83333333333333337</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>289</v>
+        <v>199</v>
+      </c>
+      <c r="I134" s="10">
+        <v>1.8333333333333335</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K134" s="6"/>
     </row>
@@ -7143,31 +6941,31 @@
         <v>36877</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>618</v>
+        <v>511</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>619</v>
+        <v>512</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>171</v>
+        <v>14</v>
+      </c>
+      <c r="G135" s="10">
+        <v>3.1666666666666665</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
+      </c>
+      <c r="I135" s="10">
+        <v>3.25</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K135" s="6" t="s">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7178,28 +6976,28 @@
         <v>47756</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>620</v>
+        <v>513</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>621</v>
+        <v>514</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G136" s="10">
+        <v>0</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="I136" s="10">
+        <v>5.5</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K136" s="6"/>
     </row>
@@ -7211,28 +7009,28 @@
         <v>32606</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>622</v>
+        <v>515</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>623</v>
+        <v>516</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G137" s="10">
+        <v>0</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>58</v>
+        <v>201</v>
+      </c>
+      <c r="I137" s="10">
+        <v>4.5</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K137" s="6"/>
     </row>
@@ -7244,28 +7042,28 @@
         <v>94743</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>624</v>
+        <v>517</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>625</v>
+        <v>518</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G138" s="10">
+        <v>0</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="I138" s="10">
+        <v>5.5</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K138" s="6"/>
     </row>
@@ -7277,28 +7075,28 @@
         <v>69024</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>626</v>
+        <v>519</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>627</v>
+        <v>520</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G139" s="10">
+        <v>0</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>15</v>
+        <v>162</v>
+      </c>
+      <c r="I139" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K139" s="6"/>
     </row>
@@ -7310,31 +7108,31 @@
         <v>622</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>628</v>
+        <v>521</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>629</v>
+        <v>522</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>292</v>
+        <v>46</v>
+      </c>
+      <c r="G140" s="10">
+        <v>3.3333333333333335</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>61</v>
+        <v>202</v>
+      </c>
+      <c r="I140" s="10">
+        <v>8.4166666666666661</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K140" s="6" t="s">
-        <v>294</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7345,31 +7143,31 @@
         <v>4174</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>630</v>
+        <v>523</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>631</v>
+        <v>524</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G141" s="10">
+        <v>0</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
+      </c>
+      <c r="I141" s="10">
+        <v>2.4166666666666665</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K141" s="6" t="s">
-        <v>295</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7380,31 +7178,31 @@
         <v>20219</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>632</v>
+        <v>525</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>633</v>
+        <v>526</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>296</v>
+        <v>32</v>
+      </c>
+      <c r="G142" s="10">
+        <v>2.5833333333333335</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
+      </c>
+      <c r="I142" s="10">
+        <v>8.6666666666666661</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K142" s="6" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7415,31 +7213,31 @@
         <v>99130</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>634</v>
+        <v>527</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>635</v>
+        <v>528</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>299</v>
+        <v>14</v>
+      </c>
+      <c r="G143" s="10">
+        <v>2.25</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>27</v>
+        <v>207</v>
+      </c>
+      <c r="I143" s="10">
+        <v>7.5</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>301</v>
+        <v>208</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7450,31 +7248,31 @@
         <v>86220</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>636</v>
+        <v>529</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>637</v>
+        <v>530</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G144" s="10">
+        <v>0</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I144" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>302</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7485,31 +7283,31 @@
         <v>73507</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>638</v>
+        <v>531</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>639</v>
+        <v>532</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>303</v>
+        <v>10</v>
+      </c>
+      <c r="G145" s="10">
+        <v>4</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>304</v>
+        <v>142</v>
+      </c>
+      <c r="I145" s="10">
+        <v>5.416666666666667</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>305</v>
+        <v>210</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7520,28 +7318,28 @@
         <v>48380</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>640</v>
+        <v>533</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>641</v>
+        <v>534</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G146" s="10">
+        <v>0</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>15</v>
+        <v>162</v>
+      </c>
+      <c r="I146" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K146" s="6"/>
     </row>
@@ -7553,27 +7351,29 @@
         <v>44978</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>642</v>
+        <v>535</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>643</v>
+        <v>536</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>105</v>
+        <v>52</v>
+      </c>
+      <c r="G147" s="10">
+        <v>9</v>
       </c>
       <c r="H147" s="1"/>
-      <c r="I147" s="1"/>
+      <c r="I147" s="10">
+        <v>10.416666666666666</v>
+      </c>
       <c r="J147" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>306</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7584,31 +7384,31 @@
         <v>95985</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>644</v>
+        <v>537</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>645</v>
+        <v>538</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G148" s="10">
+        <v>0</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>42</v>
+        <v>212</v>
+      </c>
+      <c r="I148" s="10">
+        <v>3.3333333333333335</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K148" s="6" t="s">
-        <v>308</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7619,31 +7419,31 @@
         <v>51453</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>646</v>
+        <v>539</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>647</v>
+        <v>540</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G149" s="10">
+        <v>0</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>310</v>
+        <v>214</v>
+      </c>
+      <c r="I149" s="10">
+        <v>4.666666666666667</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7654,31 +7454,31 @@
         <v>99789</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>648</v>
+        <v>541</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>649</v>
+        <v>542</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>312</v>
+        <v>19</v>
+      </c>
+      <c r="G150" s="10">
+        <v>4</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>225</v>
+        <v>196</v>
+      </c>
+      <c r="I150" s="10">
+        <v>4.416666666666667</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>313</v>
+        <v>216</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7689,31 +7489,31 @@
         <v>32409</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>650</v>
+        <v>543</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>651</v>
+        <v>544</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G151" s="10">
+        <v>0</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>58</v>
+        <v>127</v>
+      </c>
+      <c r="I151" s="10">
+        <v>4.5</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>314</v>
+        <v>217</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7724,25 +7524,29 @@
         <v>62708</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>652</v>
+        <v>545</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>653</v>
+        <v>546</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G152" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G152" s="10">
+        <v>0</v>
+      </c>
       <c r="H152" s="1"/>
-      <c r="I152" s="1"/>
+      <c r="I152" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J152" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K152" s="6" t="s">
-        <v>315</v>
+        <v>218</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7753,31 +7557,31 @@
         <v>26763</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>654</v>
+        <v>547</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>655</v>
+        <v>548</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="G153" s="10">
+        <v>0</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>317</v>
+        <v>219</v>
+      </c>
+      <c r="I153" s="10">
+        <v>10.083333333333334</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>318</v>
+        <v>220</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7788,31 +7592,31 @@
         <v>31852</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>656</v>
+        <v>549</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>657</v>
+        <v>550</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G154" s="10">
+        <v>0</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>235</v>
+        <v>180</v>
+      </c>
+      <c r="I154" s="10">
+        <v>6.583333333333333</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K154" s="6" t="s">
-        <v>319</v>
+        <v>221</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7823,28 +7627,28 @@
         <v>92038</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>658</v>
+        <v>551</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>659</v>
+        <v>552</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G155" s="10">
+        <v>0</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="I155" s="10">
+        <v>3.4166666666666665</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K155" s="6"/>
     </row>
@@ -7856,31 +7660,31 @@
         <v>32488</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>660</v>
+        <v>553</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>661</v>
+        <v>554</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>320</v>
+        <v>46</v>
+      </c>
+      <c r="G156" s="10">
+        <v>3.75</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>322</v>
+        <v>222</v>
+      </c>
+      <c r="I156" s="10">
+        <v>10.75</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>323</v>
+        <v>223</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7891,28 +7695,28 @@
         <v>99294</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>662</v>
+        <v>555</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>663</v>
+        <v>556</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G157" s="10">
+        <v>0</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>325</v>
+        <v>224</v>
+      </c>
+      <c r="I157" s="10">
+        <v>4.583333333333333</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K157" s="6"/>
     </row>
@@ -7924,31 +7728,31 @@
         <v>49420</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>664</v>
+        <v>557</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>665</v>
+        <v>558</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>326</v>
+        <v>52</v>
+      </c>
+      <c r="G158" s="10">
+        <v>7</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>328</v>
+        <v>225</v>
+      </c>
+      <c r="I158" s="10">
+        <v>13.25</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>329</v>
+        <v>226</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7959,31 +7763,31 @@
         <v>70636</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>666</v>
+        <v>559</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>667</v>
+        <v>560</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G159" s="10">
+        <v>0</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>331</v>
+        <v>227</v>
+      </c>
+      <c r="I159" s="10">
+        <v>4.083333333333333</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>332</v>
+        <v>228</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7994,24 +7798,26 @@
         <v>61145</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>668</v>
+        <v>561</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>669</v>
+        <v>562</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>13</v>
+        <v>229</v>
+      </c>
+      <c r="G160" s="10">
+        <v>0</v>
       </c>
       <c r="H160" s="1"/>
-      <c r="I160" s="1"/>
+      <c r="I160" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J160" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K160" s="6"/>
     </row>
@@ -8023,31 +7829,31 @@
         <v>45377</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>670</v>
+        <v>563</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>671</v>
+        <v>564</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>243</v>
+        <v>55</v>
+      </c>
+      <c r="G161" s="10">
+        <v>2.0833333333333335</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>235</v>
+        <v>127</v>
+      </c>
+      <c r="I161" s="10">
+        <v>6.583333333333333</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>334</v>
+        <v>230</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8058,28 +7864,28 @@
         <v>77689</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>672</v>
+        <v>565</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>673</v>
+        <v>566</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G162" s="10">
+        <v>0</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>124</v>
+        <v>231</v>
+      </c>
+      <c r="I162" s="10">
+        <v>7.25</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K162" s="6"/>
     </row>
@@ -8091,24 +7897,28 @@
         <v>87071</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>674</v>
+        <v>567</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>675</v>
+        <v>568</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G163" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G163" s="10">
+        <v>0</v>
+      </c>
       <c r="H163" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I163" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I163" s="10">
+        <v>0.25</v>
+      </c>
       <c r="J163" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K163" s="6"/>
     </row>
@@ -8120,27 +7930,29 @@
         <v>36085</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>676</v>
+        <v>569</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>677</v>
+        <v>570</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>336</v>
+        <v>14</v>
+      </c>
+      <c r="G164" s="10">
+        <v>2.5833333333333335</v>
       </c>
       <c r="H164" s="1"/>
-      <c r="I164" s="1"/>
+      <c r="I164" s="10">
+        <v>7.416666666666667</v>
+      </c>
       <c r="J164" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>337</v>
+        <v>232</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8151,28 +7963,28 @@
         <v>42198</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>678</v>
+        <v>571</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>679</v>
+        <v>572</v>
       </c>
       <c r="E165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="10">
+        <v>0</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F165" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>15</v>
+      <c r="I165" s="10">
+        <v>1.3333333333333333</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K165" s="6"/>
     </row>
@@ -8184,31 +7996,31 @@
         <v>43857</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>680</v>
+        <v>573</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>681</v>
+        <v>574</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="G166" s="10">
+        <v>0</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>38</v>
+        <v>233</v>
+      </c>
+      <c r="I166" s="10">
+        <v>6.833333333333333</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K166" s="6" t="s">
-        <v>339</v>
+        <v>234</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8219,28 +8031,28 @@
         <v>77724</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>682</v>
+        <v>575</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>683</v>
+        <v>576</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="G167" s="10">
+        <v>0</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>310</v>
+        <v>235</v>
+      </c>
+      <c r="I167" s="10">
+        <v>4.666666666666667</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K167" s="6"/>
     </row>
@@ -8252,31 +8064,31 @@
         <v>32841</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>684</v>
+        <v>577</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>685</v>
+        <v>578</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>254</v>
+        <v>19</v>
+      </c>
+      <c r="G168" s="10">
+        <v>1.6666666666666665</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>157</v>
+        <v>236</v>
+      </c>
+      <c r="I168" s="10">
+        <v>7.75</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K168" s="6" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8287,31 +8099,31 @@
         <v>1554</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>686</v>
+        <v>579</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>687</v>
+        <v>580</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G169" s="10">
+        <v>0</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>344</v>
+        <v>238</v>
+      </c>
+      <c r="I169" s="10">
+        <v>4.75</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>345</v>
+        <v>239</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8322,31 +8134,31 @@
         <v>12979</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>688</v>
+        <v>581</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>689</v>
+        <v>582</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G170" s="10">
+        <v>0</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I170" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I170" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K170" s="6" t="s">
-        <v>346</v>
+        <v>240</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8357,28 +8169,28 @@
         <v>40457</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>690</v>
+        <v>583</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>691</v>
+        <v>584</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="G171" s="10">
+        <v>0</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I171" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
+      </c>
+      <c r="I171" s="10">
+        <v>2.1666666666666665</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K171" s="6"/>
     </row>
@@ -8390,31 +8202,31 @@
         <v>62957</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>692</v>
+        <v>585</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>693</v>
+        <v>586</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
+      </c>
+      <c r="G172" s="10">
+        <v>0</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
+      </c>
+      <c r="I172" s="10">
+        <v>9.9166666666666661</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K172" s="6" t="s">
-        <v>348</v>
+        <v>242</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8425,28 +8237,28 @@
         <v>12467</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>694</v>
+        <v>587</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>695</v>
+        <v>588</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G173" s="10">
+        <v>0</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>85</v>
+        <v>57</v>
+      </c>
+      <c r="I173" s="10">
+        <v>8.0833333333333339</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K173" s="6"/>
     </row>
@@ -8458,28 +8270,28 @@
         <v>93430</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>696</v>
+        <v>589</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>697</v>
+        <v>590</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="G174" s="10">
+        <v>0</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="I174" s="1" t="s">
-        <v>52</v>
+        <v>243</v>
+      </c>
+      <c r="I174" s="10">
+        <v>3.9166666666666665</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="K174" s="6"/>
     </row>
